--- a/DA418_S1_Project_Evaluation Matrix.xlsx
+++ b/DA418_S1_Project_Evaluation Matrix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\capstone-project-retail-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D24AA89-2FBF-4E1E-A759-DA4B9E82935F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D769673-AF05-4A6A-B88D-8203810F3001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{987E23C5-98A4-4861-859D-40122838D10E}"/>
   </bookViews>
@@ -1075,21 +1075,27 @@
       <c r="C12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="25"/>
       <c r="C13" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="26"/>
       <c r="C14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="2:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="24" t="s">
@@ -1359,12 +1365,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1617,20 +1625,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C224B2-9B11-4DD1-9475-843BE1A9F5EF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCFB20A3-11D3-4F21-A3E5-84487BC2ED79}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
+    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1655,12 +1664,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCFB20A3-11D3-4F21-A3E5-84487BC2ED79}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C224B2-9B11-4DD1-9475-843BE1A9F5EF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
-    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/DA418_S1_Project_Evaluation Matrix.xlsx
+++ b/DA418_S1_Project_Evaluation Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\capstone-project-retail-tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D769673-AF05-4A6A-B88D-8203810F3001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6825D44-190C-4804-9699-48E1B41E13D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{987E23C5-98A4-4861-859D-40122838D10E}"/>
   </bookViews>
@@ -1076,7 +1076,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
@@ -1085,7 +1085,7 @@
         <v>11</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
@@ -1094,7 +1094,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1365,14 +1365,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1625,21 +1623,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCFB20A3-11D3-4F21-A3E5-84487BC2ED79}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C224B2-9B11-4DD1-9475-843BE1A9F5EF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
-    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1664,9 +1661,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C224B2-9B11-4DD1-9475-843BE1A9F5EF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCFB20A3-11D3-4F21-A3E5-84487BC2ED79}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
+    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>